--- a/participantes.xlsx
+++ b/participantes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo LOQ\Desktop\Prueba 7\raceDetector\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3349A4A4-32F7-4B19-8CDD-0FF8049292B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40E1316-4B65-4B50-BEBB-EFA4020F3F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>Cédula</t>
   </si>
@@ -169,7 +169,7 @@
     <t>555-6789</t>
   </si>
   <si>
-    <t>077</t>
+    <t>777</t>
   </si>
   <si>
     <t>22334455</t>
@@ -287,13 +287,22 @@
   </si>
   <si>
     <t>dfsfds</t>
+  </si>
+  <si>
+    <t>Ramods</t>
+  </si>
+  <si>
+    <t>fdnksf</t>
+  </si>
+  <si>
+    <t>gsv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,8 +338,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,6 +357,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
         <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -374,7 +396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -384,6 +406,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -686,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -872,7 +896,7 @@
       <c r="E8" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
@@ -1084,6 +1108,29 @@
       </c>
       <c r="G17">
         <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1451</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/participantes.xlsx
+++ b/participantes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo LOQ\Desktop\Prueba 7\raceDetector\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40E1316-4B65-4B50-BEBB-EFA4020F3F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D54DE6F-DD85-4F10-A241-828824CB863C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="96">
   <si>
     <t>Cédula</t>
   </si>
@@ -296,6 +296,18 @@
   </si>
   <si>
     <t>gsv</t>
+  </si>
+  <si>
+    <t>marlos</t>
+  </si>
+  <si>
+    <t>fdgsgfs</t>
+  </si>
+  <si>
+    <t>gfdsgd</t>
+  </si>
+  <si>
+    <t>ggds</t>
   </si>
 </sst>
 </file>
@@ -710,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1130,6 +1142,29 @@
         <v>12</v>
       </c>
       <c r="G18">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>180222</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19">
         <v>101</v>
       </c>
     </row>

--- a/participantes.xlsx
+++ b/participantes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo LOQ\Desktop\Prueba 7\raceDetector\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D54DE6F-DD85-4F10-A241-828824CB863C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97A450E-18C4-4457-9031-DB0D2B5EAD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1142,7 +1142,7 @@
         <v>12</v>
       </c>
       <c r="G18">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">

--- a/participantes.xlsx
+++ b/participantes.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,32 +39,11 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00006100"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -75,24 +54,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
         <bgColor rgb="FF4472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -120,19 +81,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,19 +453,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="7"/>
+    <col width="15.109375" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30.33203125" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="13.44140625" customWidth="1" min="8" max="8"/>
+    <col width="12.5546875" customWidth="1" min="9" max="9"/>
+    <col width="16.6640625" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.6" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cédula</t>
+          <t>Cedula</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -525,22 +485,37 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Dirección</t>
+          <t>Edad</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Distancia</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Contacto</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dorsal</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Estado Pago</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Número Dorsal</t>
         </is>
       </c>
     </row>
@@ -590,7 +565,59 @@
           <t>100</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>PAGADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20K</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>manuel@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>JUVENIL</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>PAGADO</t>
         </is>
